--- a/www/download/IND.gross_output.s.mv.zdW13.xlsx
+++ b/www/download/IND.gross_output.s.mv.zdW13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15118.631</t>
+          <t>15118631344.5598</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15355.088</t>
+          <t>15355087721.2444</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15278.993</t>
+          <t>15278993052.529</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15408.142</t>
+          <t>15408142204.0692</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16188.49</t>
+          <t>16188490149.3482</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>15680.2</t>
+          <t>15680199673.1464</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15268.856</t>
+          <t>15268855654.1273</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16026.905</t>
+          <t>16026904623.0148</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16804.38</t>
+          <t>16804380372.78</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>18534.433</t>
+          <t>18534433215.5633</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>18847.172</t>
+          <t>18847171957.7447</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19294.52</t>
+          <t>19294519805.4491</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20311.255</t>
+          <t>20311254522.9583</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>21445.495</t>
+          <t>21445495328.7561</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>21923.779</t>
+          <t>21923779278.715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7497.653</t>
+          <t>7497652914.42103</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7732.664</t>
+          <t>7732663678.20522</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7286.548</t>
+          <t>7286547536.294</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7446.902</t>
+          <t>7446902130.91801</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7488.223</t>
+          <t>7488223069.0661</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7919.681</t>
+          <t>7919681003.77256</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8060.055</t>
+          <t>8060055221.47362</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7837.8</t>
+          <t>7837800016.58909</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8116.463</t>
+          <t>8116462880.89045</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>8405.654</t>
+          <t>8405653600.4791</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>8268.991</t>
+          <t>8268991274.22517</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>8986.25</t>
+          <t>8986249619.91559</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>9287.749</t>
+          <t>9287748587.89852</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>9830.592</t>
+          <t>9830591588.86675</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>8444.747</t>
+          <t>8444747446.74592</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9561.278</t>
+          <t>9561277790.70018</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8967.786</t>
+          <t>8967786461.44638</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8615.054</t>
+          <t>8615053792.51127</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8743.943</t>
+          <t>8743942759.39498</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8817.831</t>
+          <t>8817830762.80937</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9589.28</t>
+          <t>9589279577.18918</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>9527.632</t>
+          <t>9527632144.6464</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9222.237</t>
+          <t>9222237189.66084</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9906.251</t>
+          <t>9906251051.95125</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10449.898</t>
+          <t>10449898401.1063</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10002.168</t>
+          <t>10002168010.6904</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10811.617</t>
+          <t>10811616938.52</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>11385.209</t>
+          <t>11385208650.8527</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>13566.541</t>
+          <t>13566541133.8166</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10051.414</t>
+          <t>10051414222.5481</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6886.956</t>
+          <t>6886955600.59111</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7207.419</t>
+          <t>7207419430.47789</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6621.463</t>
+          <t>6621462795.71029</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6296.944</t>
+          <t>6296944084.28997</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5882.479</t>
+          <t>5882478936.91973</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5597.377</t>
+          <t>5597377149.48479</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5357.934</t>
+          <t>5357934462.9873</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5286.839</t>
+          <t>5286838548.4719</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5456.876</t>
+          <t>5456875614.92465</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5857.148</t>
+          <t>5857148145.41522</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5969.682</t>
+          <t>5969681513.77597</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6339.593</t>
+          <t>6339592950.38071</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6529.871</t>
+          <t>6529870999.79063</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6522.589</t>
+          <t>6522589139.63906</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>6411.183</t>
+          <t>6411182500.71277</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>141916.195</t>
+          <t>141916195499.364</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>140367.251</t>
+          <t>140367250747.366</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>139942.597</t>
+          <t>139942596674.318</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>136410.301</t>
+          <t>136410300937.414</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>139810.796</t>
+          <t>139810795754.628</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>142252.404</t>
+          <t>142252404146.283</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>137940.626</t>
+          <t>137940625727.165</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>141882.96</t>
+          <t>141882960189.742</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>145984.547</t>
+          <t>145984547070</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>153659.599</t>
+          <t>153659598819.449</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>156530.566</t>
+          <t>156530565942.895</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>155503.727</t>
+          <t>155503727427.966</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>158162.249</t>
+          <t>158162249055.674</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>162572.326</t>
+          <t>162572325678.306</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>155062.805</t>
+          <t>155062804751.653</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22926.401</t>
+          <t>22926401342.4255</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23393.047</t>
+          <t>23393047148.8587</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23193.963</t>
+          <t>23193962747.0067</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23395.733</t>
+          <t>23395733148.2559</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>24727.143</t>
+          <t>24727143171.0065</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27231.804</t>
+          <t>27231804423.0931</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27462.149</t>
+          <t>27462149030.9869</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26627.768</t>
+          <t>26627767780.2661</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27601.692</t>
+          <t>27601691539.8955</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30046.442</t>
+          <t>30046441924.0202</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30766.287</t>
+          <t>30766287478.7462</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>31533.798</t>
+          <t>31533797774.7127</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>30501.54</t>
+          <t>30501539917.3893</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>31212.594</t>
+          <t>31212593901.1659</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28475.721</t>
+          <t>28475720754.4226</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1725219.325</t>
+          <t>1725219325362.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1778401.586</t>
+          <t>1778401585596.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1785624.79</t>
+          <t>1785624789533.24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1788760.089</t>
+          <t>1788760089294.38</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1773854.572</t>
+          <t>1773854572366.88</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1764015.653</t>
+          <t>1764015652623.36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1805324.823</t>
+          <t>1805324823419.12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1844118.211</t>
+          <t>1844118210794.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1962531.215</t>
+          <t>1962531215064.65</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2011843.33</t>
+          <t>2011843330397.64</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2122047.377</t>
+          <t>2122047376794.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2340062.3</t>
+          <t>2340062299766.25</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2457400.03</t>
+          <t>2457400029665.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2558257.728</t>
+          <t>2558257728122.58</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2596542.15</t>
+          <t>2596542150413.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>521.77</t>
+          <t>521769635.911713</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>575.275</t>
+          <t>575275302.286532</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>511.188</t>
+          <t>511188095.686683</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>516.893</t>
+          <t>516893321.414564</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>554.528</t>
+          <t>554528136.075119</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>551.25</t>
+          <t>551250148.01107</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>613.085</t>
+          <t>613085461.082389</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>634.759</t>
+          <t>634759095.068938</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>655.663</t>
+          <t>655663296.297158</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>623.548</t>
+          <t>623547900.758255</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>575.806</t>
+          <t>575805981.170818</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>592.643</t>
+          <t>592642681.030207</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>572.893</t>
+          <t>572892568.420622</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>806.854</t>
+          <t>806853858.592282</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>568.208</t>
+          <t>568208259.113876</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11896.829</t>
+          <t>11896828949.7572</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12008.962</t>
+          <t>12008962189.3661</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12059.733</t>
+          <t>12059733358.6253</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11871.526</t>
+          <t>11871525933.7446</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11452.829</t>
+          <t>11452828616.6649</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11082.359</t>
+          <t>11082359205.2714</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11206.42</t>
+          <t>11206420324.0133</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11304.352</t>
+          <t>11304352239.2366</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11288.293</t>
+          <t>11288292689.9529</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11637.768</t>
+          <t>11637768197.7029</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11690.998</t>
+          <t>11690997664.0313</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>12611.502</t>
+          <t>12611501825.7834</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>13135.859</t>
+          <t>13135858935.1004</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>13778.288</t>
+          <t>13778287726.2227</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11525.256</t>
+          <t>11525255767.9424</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>72389.762</t>
+          <t>72389762454.2395</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>66805.841</t>
+          <t>66805841287.5726</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63726.939</t>
+          <t>63726939060.3875</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>66053.618</t>
+          <t>66053618314.3027</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>66194.42</t>
+          <t>66194420150.4384</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>69960.666</t>
+          <t>69960666490.0388</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>66600.504</t>
+          <t>66600504264.6032</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>63704.42</t>
+          <t>63704420449.0245</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>68145.661</t>
+          <t>68145661130.6113</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>71544.644</t>
+          <t>71544644324.4334</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>70684.882</t>
+          <t>70684882283.4497</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>74998.583</t>
+          <t>74998583193.486</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>78948.727</t>
+          <t>78948727034.0849</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>79952.351</t>
+          <t>79952351047.7453</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>67029.652</t>
+          <t>67029652141.5665</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6030.207</t>
+          <t>6030207083.63668</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5981.284</t>
+          <t>5981284293.49359</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5717.236</t>
+          <t>5717235897.08775</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5772.804</t>
+          <t>5772803756.0448</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5421.401</t>
+          <t>5421400664.56185</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5534.777</t>
+          <t>5534776887.21488</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5700.985</t>
+          <t>5700985123.13482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5625.843</t>
+          <t>5625842624.79155</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5928.369</t>
+          <t>5928368723.82849</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>6019.243</t>
+          <t>6019243182.148</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5881.995</t>
+          <t>5881994500.39311</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>6070.11</t>
+          <t>6070109748.40437</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>6199.155</t>
+          <t>6199154550.66494</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6379.08</t>
+          <t>6379080273.47719</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5451.671</t>
+          <t>5451670787.15199</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28957.143</t>
+          <t>28957143355.0044</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28906.753</t>
+          <t>28906753311.4081</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27762.262</t>
+          <t>27762262197.4722</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29626.744</t>
+          <t>29626743623.3346</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>31875.343</t>
+          <t>31875343369.8117</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>34466.872</t>
+          <t>34466871652.0387</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>34953.758</t>
+          <t>34953757676.1277</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>36763</t>
+          <t>36763000369.7784</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>37696.025</t>
+          <t>37696024987.3377</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>39468.724</t>
+          <t>39468724427.6915</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>41197.32</t>
+          <t>41197320022.5313</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>43171.773</t>
+          <t>43171773421.2353</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44099.175</t>
+          <t>44099174585.1212</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>44761.059</t>
+          <t>44761059480.3308</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>35605.897</t>
+          <t>35605897092.4866</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1325.804</t>
+          <t>1325804114.02388</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1296.96</t>
+          <t>1296960141.31526</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1348.145</t>
+          <t>1348144759.04814</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1370.031</t>
+          <t>1370030829.9704</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1252.426</t>
+          <t>1252425780.88412</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1330.035</t>
+          <t>1330034678.96388</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1421.906</t>
+          <t>1421906222.59182</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1502.03</t>
+          <t>1502030158.32588</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1589.216</t>
+          <t>1589216227.94587</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1698.317</t>
+          <t>1698316986.6063</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1581.278</t>
+          <t>1581277868.22874</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1625.88</t>
+          <t>1625879817.1346</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1511.665</t>
+          <t>1511664865.19546</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1455.219</t>
+          <t>1455218990.07625</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1168.756</t>
+          <t>1168756327.22761</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5389.343</t>
+          <t>5389342853.80161</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5489.25</t>
+          <t>5489250118.03929</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5472.622</t>
+          <t>5472622346.82475</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5822.519</t>
+          <t>5822518656.31032</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6234.286</t>
+          <t>6234286167.28732</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6264.239</t>
+          <t>6264239325.4069</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5900.297</t>
+          <t>5900296539.87156</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5859.764</t>
+          <t>5859764078.52474</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6076.557</t>
+          <t>6076556831.02956</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>6286.048</t>
+          <t>6286048035.73885</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6519.287</t>
+          <t>6519287470.65051</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6775.312</t>
+          <t>6775312359.13568</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6923.548</t>
+          <t>6923547802.76809</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>7284.08</t>
+          <t>7284080063.64278</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5438.157</t>
+          <t>5438156536.66287</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>41091.706</t>
+          <t>41091706309.6693</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40003.63</t>
+          <t>40003629823.0411</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36898.44</t>
+          <t>36898440261.1629</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38123.244</t>
+          <t>38123244478.6612</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>40311.494</t>
+          <t>40311494420.6683</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>41923.311</t>
+          <t>41923311116.9155</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>41649.944</t>
+          <t>41649943762.5992</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>40333.255</t>
+          <t>40333254865.8457</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>41938.831</t>
+          <t>41938830859.556</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>43080.275</t>
+          <t>43080275179.2446</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>43534.702</t>
+          <t>43534701994.7151</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>44406.182</t>
+          <t>44406181910.9556</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>45576.723</t>
+          <t>45576723286.646</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>47476.893</t>
+          <t>47476893385.6499</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>41895.142</t>
+          <t>41895142420.749</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>44397.465</t>
+          <t>44397465365.3051</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45027.395</t>
+          <t>45027395024.3677</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>43292.729</t>
+          <t>43292729165.2627</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42862.484</t>
+          <t>42862483605.6242</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>42357.105</t>
+          <t>42357105064.5474</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>42148.377</t>
+          <t>42148377024.2858</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>41640.133</t>
+          <t>41640132541.8114</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>40781.409</t>
+          <t>40781409193.5602</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>41436.342</t>
+          <t>41436342296.3957</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>43384.875</t>
+          <t>43384875459.9721</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>44370.39</t>
+          <t>44370390123.3153</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>45192.565</t>
+          <t>45192565366.3224</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>45022.341</t>
+          <t>45022340644.2437</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>43168.05</t>
+          <t>43168050019.2774</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>38946.02</t>
+          <t>38946019925.0441</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8878.965</t>
+          <t>8878964855.36884</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9073.253</t>
+          <t>9073253482.17552</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8352.147</t>
+          <t>8352146525.33614</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>8288.387</t>
+          <t>8288386965.54645</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8332.98</t>
+          <t>8332980213.58659</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8933.19</t>
+          <t>8933190110.29848</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8519.286</t>
+          <t>8519286436.74094</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8484.473</t>
+          <t>8484472500.57733</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8419.285</t>
+          <t>8419285166.7311</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>8204.272</t>
+          <t>8204271502.85996</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8207.192</t>
+          <t>8207192301.755</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8786.912</t>
+          <t>8786912097.22568</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>8775.677</t>
+          <t>8775677383.04753</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8828.754</t>
+          <t>8828753558.99991</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8035.53</t>
+          <t>8035530477.65771</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9011.844</t>
+          <t>9011843525.3821</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9108.417</t>
+          <t>9108417077.86287</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8814.969</t>
+          <t>8814968906.16341</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9003.604</t>
+          <t>9003604242.85882</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>9526.867</t>
+          <t>9526866884.72961</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9538.612</t>
+          <t>9538611799.63991</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9299.336</t>
+          <t>9299335655.47531</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9262.15</t>
+          <t>9262150437.63694</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>9241.317</t>
+          <t>9241316622.48889</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8826.314</t>
+          <t>8826314096.82981</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8682.682</t>
+          <t>8682681688.30664</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8788.694</t>
+          <t>8788694290.00647</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8985.17</t>
+          <t>8985169866.37776</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8722</t>
+          <t>8721999759.12168</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7846.054</t>
+          <t>7846053841.91154</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>136666.667</t>
+          <t>136666666572.902</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>141691.523</t>
+          <t>141691523343.883</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>137485.915</t>
+          <t>137485915465.221</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>129631.569</t>
+          <t>129631569232.571</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>146473.525</t>
+          <t>146473524820.161</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>154417.353</t>
+          <t>154417353062.108</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>158079.924</t>
+          <t>158079923948.193</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>167760.271</t>
+          <t>167760271004.454</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>173874.497</t>
+          <t>173874496500.434</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>171942.188</t>
+          <t>171942187800.763</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>153046.533</t>
+          <t>153046533457.818</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>147190.26</t>
+          <t>147190260001.273</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>153676.691</t>
+          <t>153676690965.94</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>156987.039</t>
+          <t>156987038515.63</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>164984.107</t>
+          <t>164984107435.899</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1110246.475</t>
+          <t>1110246475344.09</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1126960.353</t>
+          <t>1126960353153.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1147275.355</t>
+          <t>1147275355184.24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1145281.411</t>
+          <t>1145281410896.73</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1107868.219</t>
+          <t>1107868219276.62</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1155618.154</t>
+          <t>1155618153599.04</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1191151.068</t>
+          <t>1191151068308.79</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1176173.701</t>
+          <t>1176173701166.22</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1269571.106</t>
+          <t>1269571105786.43</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1303778.667</t>
+          <t>1303778667012.83</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1332678.901</t>
+          <t>1332678900654.43</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1349410.741</t>
+          <t>1349410740777.78</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1309768.231</t>
+          <t>1309768230606.79</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1301918.854</t>
+          <t>1301918853910.27</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1323732.066</t>
+          <t>1323732065945.18</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3858.377</t>
+          <t>3858376862.64709</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3960.945</t>
+          <t>3960945477.4173</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3881.385</t>
+          <t>3881385193.77535</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3870.935</t>
+          <t>3870934511.13001</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4257.394</t>
+          <t>4257393988.85815</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4576.705</t>
+          <t>4576705395.89683</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4717.902</t>
+          <t>4717901843.90763</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4478.362</t>
+          <t>4478362364.8118</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4761.702</t>
+          <t>4761702029.3472</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5218.035</t>
+          <t>5218035489.04</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5490.897</t>
+          <t>5490896950.36072</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>5746.456</t>
+          <t>5746455917.02659</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>5941.751</t>
+          <t>5941750937.30658</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5564.164</t>
+          <t>5564163968.09739</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4904.989</t>
+          <t>4904989018.55887</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>49874.97</t>
+          <t>49874969554.6232</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49344.427</t>
+          <t>49344427430.4855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46931.762</t>
+          <t>46931762112.5945</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>48313.435</t>
+          <t>48313435322.7035</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>48605.836</t>
+          <t>48605835596.4291</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>51525.097</t>
+          <t>51525097107.3097</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>51293.799</t>
+          <t>51293798822.0109</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>50632.32</t>
+          <t>50632319813.612</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>52513.435</t>
+          <t>52513434934.3098</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>54727.991</t>
+          <t>54727990678.2597</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>54309.239</t>
+          <t>54309239002.2856</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>58514.261</t>
+          <t>58514261363.5063</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>58844.263</t>
+          <t>58844262779.5437</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>59506.576</t>
+          <t>59506576141.6352</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>48538.509</t>
+          <t>48538508718.8212</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>172758.677</t>
+          <t>172758676982.736</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>164891.73</t>
+          <t>164891729976.292</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>157870.962</t>
+          <t>157870961645.004</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>142348.147</t>
+          <t>142348146542.183</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>142965.75</t>
+          <t>142965750229.213</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>149121.911</t>
+          <t>149121911407.102</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>142316.326</t>
+          <t>142316325866.072</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>135113.682</t>
+          <t>135113682132.893</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>139843.844</t>
+          <t>139843844012.504</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>146313.392</t>
+          <t>146313391671.593</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>145715.228</t>
+          <t>145715227607.709</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>150680.074</t>
+          <t>150680073795.996</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>148570.543</t>
+          <t>148570542571.528</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>153504.169</t>
+          <t>153504168664.673</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>126049.552</t>
+          <t>126049551814.432</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>72530.622</t>
+          <t>72530621646.4814</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>72342.67</t>
+          <t>72342669684.4426</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>70591.769</t>
+          <t>70591769493.0299</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60774.869</t>
+          <t>60774869450.3709</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65208.317</t>
+          <t>65208317375.6704</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>70279.164</t>
+          <t>70279164196.8271</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>68338.961</t>
+          <t>68338960939.0107</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>69546.694</t>
+          <t>69546693534.744</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>71901.676</t>
+          <t>71901675686.2549</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>77849.403</t>
+          <t>77849402512.3985</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>77331.555</t>
+          <t>77331555489.0592</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>81063.686</t>
+          <t>81063686250.4771</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>81209.24</t>
+          <t>81209240393.7991</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>84624.881</t>
+          <t>84624880738.6454</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>77263.882</t>
+          <t>77263882262.5845</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2976.105</t>
+          <t>2976105427.1958</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2930.064</t>
+          <t>2930063990.15321</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2636.634</t>
+          <t>2636634010.2104</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2821.328</t>
+          <t>2821328470.98746</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2635.078</t>
+          <t>2635078102.13662</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2708.607</t>
+          <t>2708607390.92052</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2637.935</t>
+          <t>2637935396.5157</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2669.121</t>
+          <t>2669120596.62752</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2772.784</t>
+          <t>2772783808.7137</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2658.31</t>
+          <t>2658309601.11984</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2783.95</t>
+          <t>2783949930.77216</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2749.481</t>
+          <t>2749480786.89653</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2804.401</t>
+          <t>2804401292.36203</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2949.137</t>
+          <t>2949136757.28203</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2505.782</t>
+          <t>2505781910.51527</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>397.827</t>
+          <t>397826598.34895</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>355.237</t>
+          <t>355236563.248389</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>331.541</t>
+          <t>331541302.887578</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>358.057</t>
+          <t>358057044.02391</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>329.982</t>
+          <t>329981544.335533</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>370.214</t>
+          <t>370214054.431011</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>354.502</t>
+          <t>354502424.785215</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>362.97</t>
+          <t>362970313.399289</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>413.518</t>
+          <t>413517524.546892</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>460.653</t>
+          <t>460652842.759147</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>465.01</t>
+          <t>465009552.747234</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>482.561</t>
+          <t>482560507.700891</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>480.925</t>
+          <t>480925197.227611</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>507.455</t>
+          <t>507454611.371219</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>466.578</t>
+          <t>466577634.801283</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1399.913</t>
+          <t>1399912669.32053</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1373.151</t>
+          <t>1373150887.3834</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1408.84</t>
+          <t>1408839550.00929</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1422.537</t>
+          <t>1422536695.02309</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1318.016</t>
+          <t>1318015547.33998</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1191.255</t>
+          <t>1191255217.82963</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1189.203</t>
+          <t>1189203018.86454</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1190.63</t>
+          <t>1190629567.27547</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1298.341</t>
+          <t>1298341083.03832</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1403.353</t>
+          <t>1403352801.56579</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1447.985</t>
+          <t>1447985335.51281</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1554.886</t>
+          <t>1554886425.78916</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1714.152</t>
+          <t>1714152190.38285</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1536.246</t>
+          <t>1536246036.27336</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1083.924</t>
+          <t>1083923981.42932</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>63283.707</t>
+          <t>63283706897.0449</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>66343.364</t>
+          <t>66343364242.8948</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>65382.084</t>
+          <t>65382083783.172</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>68535.227</t>
+          <t>68535227110.4229</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>71221.912</t>
+          <t>71221911934.5639</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>73676.233</t>
+          <t>73676232562.2446</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>74912.55</t>
+          <t>74912549692.6918</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>74601.588</t>
+          <t>74601588425.7502</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>76550.27</t>
+          <t>76550269919.9621</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>80480.846</t>
+          <t>80480846077.1739</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>80987.363</t>
+          <t>80987363178.6607</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>81340.356</t>
+          <t>81340356445.8745</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>80685.16</t>
+          <t>80685159651.5548</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>86298.995</t>
+          <t>86298994506.9813</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>83152.72</t>
+          <t>83152720479.9713</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>271.751</t>
+          <t>271750544.163071</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>270.454</t>
+          <t>270454296.618474</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>236.256</t>
+          <t>236256219.489866</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>251.103</t>
+          <t>251102892.987624</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>280.945</t>
+          <t>280944728.966092</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>315.209</t>
+          <t>315208982.391996</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>261.733</t>
+          <t>261732711.820202</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>275.793</t>
+          <t>275793329.691524</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>277.851</t>
+          <t>277851166.282727</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>264.295</t>
+          <t>264294975.424329</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>246.15</t>
+          <t>246149970.735061</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>272.283</t>
+          <t>272283222.050636</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>274.035</t>
+          <t>274034564.968602</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>284.179</t>
+          <t>284179390.577359</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>246.203</t>
+          <t>246203468.780252</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18416.421</t>
+          <t>18416421178.5935</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18876.013</t>
+          <t>18876013210.4052</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>17299.033</t>
+          <t>17299033391.6668</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19300.289</t>
+          <t>19300288717.7136</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>20477999918.8423</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>20437.579</t>
+          <t>20437578511.2837</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21293.576</t>
+          <t>21293575911.1572</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>18040.662</t>
+          <t>18040662240.3964</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>21973.053</t>
+          <t>21973053352.4682</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>22099.864</t>
+          <t>22099863625.4223</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>22998.126</t>
+          <t>22998126311.1988</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23117.405</t>
+          <t>23117404536.888</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24208.397</t>
+          <t>24208397393.3129</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>26924.307</t>
+          <t>26924306780.3156</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>23516.706</t>
+          <t>23516705805.3819</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35747.219</t>
+          <t>35747218546.8067</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>36394.578</t>
+          <t>36394577695.7202</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35574.371</t>
+          <t>35574370771.2059</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>35493.288</t>
+          <t>35493288338.6088</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>33763.822</t>
+          <t>33763822194.8833</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>34264.253</t>
+          <t>34264253024.9869</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29568.311</t>
+          <t>29568310534.3318</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>28067.019</t>
+          <t>28067019304.9428</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>27778.555</t>
+          <t>27778554557.0342</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>28540.892</t>
+          <t>28540892181.1577</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>29185.085</t>
+          <t>29185085001.2887</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>30468.333</t>
+          <t>30468332701.1144</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>32335.518</t>
+          <t>32335518177.0485</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>34221.058</t>
+          <t>34221058496.9472</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>30963.939</t>
+          <t>30963938776.3773</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>11312.789</t>
+          <t>11312788524.7395</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11221.084</t>
+          <t>11221084140.4574</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>10628.592</t>
+          <t>10628592324.7295</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11147.693</t>
+          <t>11147693200.5796</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11083.101</t>
+          <t>11083101493.9354</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11798.658</t>
+          <t>11798657760.4674</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>11797.495</t>
+          <t>11797495374.3793</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11464.787</t>
+          <t>11464786993.4887</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>11280.269</t>
+          <t>11280268701.5339</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>11458.877</t>
+          <t>11458876525.43</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>11014.521</t>
+          <t>11014521118.8365</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10985.264</t>
+          <t>10985263606.9996</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>11261.405</t>
+          <t>11261405425.6269</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>11481.814</t>
+          <t>11481814306.3571</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>9918.258</t>
+          <t>9918257953.12954</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>25127.069</t>
+          <t>25127068975.8773</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>26445.591</t>
+          <t>26445590539.1822</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>23795.64</t>
+          <t>23795639796.6386</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21840.417</t>
+          <t>21840417036.3187</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>27425.519</t>
+          <t>27425519202.2057</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>26596.499</t>
+          <t>26596499241.1202</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>25878.662</t>
+          <t>25878662442.9065</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22076.859</t>
+          <t>22076858663.7198</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21746.261</t>
+          <t>21746261405.2019</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>20917.54</t>
+          <t>20917540453.8479</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20670.088</t>
+          <t>20670088311.3483</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>20674.893</t>
+          <t>20674892760.6024</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20925.587</t>
+          <t>20925586729.9547</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>21040.435</t>
+          <t>21040435084.518</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>19903.84</t>
+          <t>19903840111.4744</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>170878.701</t>
+          <t>170878701418.329</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>169972.268</t>
+          <t>169972267982.772</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>159442.856</t>
+          <t>159442855786.505</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>148828.722</t>
+          <t>148828721565.318</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>143892.827</t>
+          <t>143892826632.776</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>147731.147</t>
+          <t>147731146740.395</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>149910.232</t>
+          <t>149910231613.713</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>145957.963</t>
+          <t>145957962801.649</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>146417.332</t>
+          <t>146417332196.96</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>144241.186</t>
+          <t>144241185554.42</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>143933.911</t>
+          <t>143933911449.122</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>140990.097</t>
+          <t>140990096869.905</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>146529.983</t>
+          <t>146529983105.538</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>147607.644</t>
+          <t>147607643744.98</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>144611.281</t>
+          <t>144611281483.812</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4894.586</t>
+          <t>4894586195.66506</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4880.456</t>
+          <t>4880456408.08832</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4546.941</t>
+          <t>4546941144.05387</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4392.198</t>
+          <t>4392197915.25371</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4196.273</t>
+          <t>4196273470.58462</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4183.468</t>
+          <t>4183467572.86371</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4178.304</t>
+          <t>4178304426.55323</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4014.582</t>
+          <t>4014582458.42184</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4091.256</t>
+          <t>4091255864.92249</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4181.843</t>
+          <t>4181842873.01594</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4309.183</t>
+          <t>4309182537.69569</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4632.102</t>
+          <t>4632102168.98523</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5123.568</t>
+          <t>5123567537.63353</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5281.747</t>
+          <t>5281747312.27802</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4906.192</t>
+          <t>4906191879.27833</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2271.737</t>
+          <t>2271737317.55048</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2212.462</t>
+          <t>2212462277.53077</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2068.5</t>
+          <t>2068500113.47739</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2081.133</t>
+          <t>2081133071.28026</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2084.074</t>
+          <t>2084073698.62559</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2178.752</t>
+          <t>2178751872.81576</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2185.971</t>
+          <t>2185970776.91513</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2161.117</t>
+          <t>2161116828.80111</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2271.908</t>
+          <t>2271907977.16954</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2250.577</t>
+          <t>2250576644.27981</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2222.37</t>
+          <t>2222370142.61307</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2301.628</t>
+          <t>2301628466.09459</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2402.26</t>
+          <t>2402259919.54358</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2590.361</t>
+          <t>2590360643.68915</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2239.901</t>
+          <t>2239901337.43184</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8448.187</t>
+          <t>8448187293.99626</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8130.39</t>
+          <t>8130389601.20029</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7874.064</t>
+          <t>7874064410.13992</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>8199.649</t>
+          <t>8199648682.78154</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8317.387</t>
+          <t>8317386562.2485</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8929.258</t>
+          <t>8929258138.93522</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8496.137</t>
+          <t>8496136833.97072</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8281.26</t>
+          <t>8281259554.57812</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8588.342</t>
+          <t>8588341588.72548</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8905.853</t>
+          <t>8905853493.91647</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9132.499</t>
+          <t>9132499406.35747</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>9280.963</t>
+          <t>9280962511.49692</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>9761.026</t>
+          <t>9761026395.42823</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>9789.995</t>
+          <t>9789994702.29348</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8219.988</t>
+          <t>8219987571.43325</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>49352.967</t>
+          <t>49352966747.0967</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50628.842</t>
+          <t>50628842468.7746</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>51476.983</t>
+          <t>51476982504.1388</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>50435.638</t>
+          <t>50435637857.4576</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>51304.681</t>
+          <t>51304681390.8278</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50966.908</t>
+          <t>50966908316.9285</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>49455.174</t>
+          <t>49455173920.1404</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>49894.099</t>
+          <t>49894099141.1911</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>51460.003</t>
+          <t>51460002596.5931</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53476.965</t>
+          <t>53476964765.9664</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>53087.54</t>
+          <t>53087539707.3778</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>51515.825</t>
+          <t>51515825139.3411</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>50618.32</t>
+          <t>50618320317.8358</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>54022.002</t>
+          <t>54022002152.4216</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>47326.741</t>
+          <t>47326740858.9534</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31231.585</t>
+          <t>31231585448.0214</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>30486.561</t>
+          <t>30486561372.5302</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>29589.204</t>
+          <t>29589203991.0657</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>28627.455</t>
+          <t>28627455448.0538</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>28362.477</t>
+          <t>28362477316.2937</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>30411.25</t>
+          <t>30411249505.6038</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>27203.884</t>
+          <t>27203883555.0863</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>28587.535</t>
+          <t>28587534790.3648</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>30181.84</t>
+          <t>30181840161.5386</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>33837.209</t>
+          <t>33837208929.9333</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>32699.101</t>
+          <t>32699101136.8232</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>33627.863</t>
+          <t>33627863165.0621</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>33590.98</t>
+          <t>33590980476.7807</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>34132.324</t>
+          <t>34132323960.8041</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>27785.692</t>
+          <t>27785691617.5086</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222580.217</t>
+          <t>222580217061.596</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>224348.993</t>
+          <t>224348993124.874</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>227821.458</t>
+          <t>227821458200.902</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>232380.024</t>
+          <t>232380024339.821</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>240263.633</t>
+          <t>240263632545.11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>254442.159</t>
+          <t>254442159223.331</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>240960.239</t>
+          <t>240960238884.802</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>231212.03</t>
+          <t>231212030120.86</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>235608.458</t>
+          <t>235608457651.317</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>250816.092</t>
+          <t>250816092158.46</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>258642.922</t>
+          <t>258642922184.539</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>265929.316</t>
+          <t>265929316204.411</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>256463.971</t>
+          <t>256463971058.941</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>255910.712</t>
+          <t>255910711762.612</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>211189.267</t>
+          <t>211189267198.131</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2050739.766</t>
+          <t>2050739765956.09</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2097344.068</t>
+          <t>2097344067954.26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2138286.852</t>
+          <t>2138286852430.43</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2174711.948</t>
+          <t>2174711948457.64</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2183529.099</t>
+          <t>2183529099155.79</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2257224.744</t>
+          <t>2257224744292.89</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2343784.886</t>
+          <t>2343784885980.23</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2421717.544</t>
+          <t>2421717544261.65</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2524777.869</t>
+          <t>2524777868950.96</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2609861.024</t>
+          <t>2609861024313.3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2675242.693</t>
+          <t>2675242693495.76</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2799468.074</t>
+          <t>2799468074300.45</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2805198.531</t>
+          <t>2805198530696.85</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2879624.773</t>
+          <t>2879624772911.33</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2965900.034</t>
+          <t>2965900033982.57</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6404283.612</t>
+          <t>6404283612120.52</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6517107.089</t>
+          <t>6517107088657.73</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6542956.816</t>
+          <t>6542956815529.25</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6546820.981</t>
+          <t>6546820981086.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6546149.08</t>
+          <t>6546149080406.34</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6716984.664</t>
+          <t>6716984664212.14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6846414.503</t>
+          <t>6846414502895.4</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6929538.765</t>
+          <t>6929538764563.77</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7288771.15</t>
+          <t>7288771149883.51</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>7515255.587</t>
+          <t>7515255586779.74</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>7712999.627</t>
+          <t>7712999626804.47</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8097548.769</t>
+          <t>8097548768919.63</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8195717.771</t>
+          <t>8195717771307.14</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8402329.358</t>
+          <t>8402329358156.24</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8379832.294</t>
+          <t>8379832294192.37</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW13</t>
